--- a/entrepreneur_forms/001_market_sizing_template--entrepreneur_forms.xlsx
+++ b/entrepreneur_forms/001_market_sizing_template--entrepreneur_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>market_sizing_template</t>
+          <t>company_info</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Market Sizing Template</t>
+          <t>Company Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,179 +543,179 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>market_size</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>What is the current market size?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>market_size</t>
+          <t>revenue_potential</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>market_size</t>
+          <t>What is the revenue potential for this market?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>growth_rate</t>
+          <t>market_entry_date</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>growth_rate</t>
+          <t>When will you enter the market?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>revenue_potential</t>
+          <t>market_exit_date</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>revenue_potential</t>
+          <t>When will you exit the market?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>market</t>
+          <t>market_exit_strategy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>market</t>
+          <t>What is your exit strategy?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>competition</t>
+          <t>entry_barriers</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>competition</t>
+          <t>What are the entry barriers for this market?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>market_entry_date</t>
+          <t>growth_rate</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>market_entry_date</t>
+          <t>What is the growth rate for this market?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>market_exit_date</t>
+          <t>total_potential</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>market_exit_date</t>
+          <t>What is the total potential for this market?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>market_exit_strategy</t>
+          <t>market_segment</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>market_exit_strategy</t>
+          <t>What market segment does this belong to?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,41 +750,41 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>entry_barrier</t>
+          <t>geographic_location</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>entry_barrier</t>
+          <t>Where is this market located?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>growth_rate</t>
+          <t>customer_segment</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>growth_rate</t>
+          <t>Which customer segment does this belong to?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,41 +796,41 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>total_potential</t>
+          <t>total_revenue</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>total_potential</t>
+          <t>What is the total revenue for this market?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>market_segment</t>
+          <t>market_presence</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>market_segment</t>
+          <t>Is the market present in this location?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,271 +842,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>geographic_location</t>
+          <t>geographic_location_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>geographic_location</t>
+          <t>Is this location within the market location?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>customer_segment</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>customer_segment</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>total_revenue</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>total_revenue</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>market_segment</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>market_segment</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>customer_segment</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>customer_segment</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>geographic_location</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>geographic_location</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>total_revenue</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>total_revenue</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>geographic_location</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>geographic_location</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>customer_segment</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>customer_segment</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>total_revenue</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>total_revenue</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>geographic_location</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>geographic_location</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1121,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1154,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'low',_'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'low', 'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1171,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'medium', 'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1188,556 +935,284 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'high',_'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'high', 'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>market_choices</t>
+          <t>market_exit_strategy_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'market_1',_'value':_'market_1'}</t>
+          <t>exit_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'market_1', 'value': 'Market 1'}</t>
+          <t>Exit 1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>market_choices</t>
+          <t>market_exit_strategy_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'market_2',_'value':_'market_2'}</t>
+          <t>exit_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'market_2', 'value': 'Market 2'}</t>
+          <t>Exit 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>market_choices</t>
+          <t>market_exit_strategy_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'market_3',_'value':_'market_3'}</t>
+          <t>exit_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'market_3', 'value': 'Market 3'}</t>
+          <t>Exit 3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>market_choices</t>
+          <t>entry_barriers_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'market_4',_'value':_'market_4'}</t>
+          <t>barrier_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'market_4', 'value': 'Market 4'}</t>
+          <t>Barrier 1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>market_choices</t>
+          <t>entry_barriers_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'market_5',_'value':_'market_5'}</t>
+          <t>barrier_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'market_5', 'value': 'Market 5'}</t>
+          <t>Barrier 2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>market_choices</t>
+          <t>entry_barriers_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'market_6',_'value':_'market_6'}</t>
+          <t>barrier_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'market_6', 'value': 'Market 6'}</t>
+          <t>Barrier 3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>market_exit_strategy_choices</t>
+          <t>market_segment_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'exit_1',_'value':_'exit_1'}</t>
+          <t>segment_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'exit_1', 'value': 'Exit 1'}</t>
+          <t>Segment 1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>market_exit_strategy_choices</t>
+          <t>market_segment_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'exit_2',_'value':_'exit_2'}</t>
+          <t>segment_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'exit_2', 'value': 'Exit 2'}</t>
+          <t>Segment 2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>market_exit_strategy_choices</t>
+          <t>geographic_location_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'exit_3',_'value':_'exit_3'}</t>
+          <t>location_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'exit_3', 'value': 'Exit 3'}</t>
+          <t>Location 1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>market_exit_strategy_choices</t>
+          <t>geographic_location_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'exit_4',_'value':_'exit_4'}</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'exit_4', 'value': 'Exit 4'}</t>
+          <t>Location 2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>market_exit_strategy_choices</t>
+          <t>customer_segment_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'exit_5',_'value':_'exit_5'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'exit_5', 'value': 'Exit 5'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>entry_barrier_choices</t>
+          <t>customer_segment_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'barrier_1',_'value':_'barrier_1'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'barrier_1', 'value': 'Barrier 1'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>entry_barrier_choices</t>
+          <t>market_presence_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'barrier_2',_'value':_'barrier_2'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'barrier_2', 'value': 'Barrier 2'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>entry_barrier_choices</t>
+          <t>market_presence_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'barrier_3',_'value':_'barrier_3'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'barrier_3', 'value': 'Barrier 3'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>market_segment_choices</t>
+          <t>geographic_location_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'segment_1',_'value':_'segment_1'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'segment_1', 'value': 'Segment 1'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>market_segment_choices</t>
+          <t>geographic_location_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'segment_2',_'value':_'segment_2'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'segment_2', 'value': 'Segment 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>geographic_location_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'location_1',_'value':_'location_1'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'location_1', 'value': 'Location 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>geographic_location_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'location_2',_'value':_'location_2'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'location_2', 'value': 'Location 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>customer_segment_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>customer_segment_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>customer_segment_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>customer_segment_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>geographic_location_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>geographic_location_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>market_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>market_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>geographic_location_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>geographic_location_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>customer_segment_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>customer_segment_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>geographic_location_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>geographic_location_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
